--- a/data/IHTM_Revenue.xlsx
+++ b/data/IHTM_Revenue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srira\Desktop\TYT DASHBOARDS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7D2507-AD53-4E63-85BE-6199BF0D4DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD00968-2300-44E1-820D-0DFC2FB3266B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Month</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Cumulative Revenue</t>
-  </si>
-  <si>
-    <t>Target Per Month</t>
   </si>
 </sst>
 </file>
@@ -390,16 +387,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
     <col min="2" max="2" width="22.7265625" customWidth="1"/>
     <col min="3" max="3" width="21.36328125" customWidth="1"/>
-    <col min="4" max="5" width="20.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -412,11 +409,8 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46113</v>
       </c>
@@ -431,7 +425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46143</v>
       </c>
@@ -443,7 +437,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46174</v>
       </c>
@@ -455,7 +449,7 @@
         <v>21.89</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46204</v>
       </c>
@@ -467,7 +461,7 @@
         <v>28.66</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46235</v>
       </c>
@@ -479,7 +473,7 @@
         <v>36.65</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46266</v>
       </c>
@@ -491,32 +485,32 @@
         <v>45.73</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46296</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46327</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46357</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46388</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46419</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46447</v>
       </c>

--- a/data/IHTM_Revenue.xlsx
+++ b/data/IHTM_Revenue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srira\Desktop\TYT DASHBOARDS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD00968-2300-44E1-820D-0DFC2FB3266B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B1B377-3CD3-4568-BC5E-E7944C8DB743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4820" yWindow="380" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue" sheetId="1" r:id="rId1"/>
